--- a/Groceries.xlsx
+++ b/Groceries.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a960143ed076ae3/Desktop/Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2328" documentId="8_{98EF138E-B783-427A-B5F9-8CBFC75A152E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C1B4B78-1526-4E41-B876-1AE47E7D0BD7}"/>
+  <xr:revisionPtr revIDLastSave="2739" documentId="8_{98EF138E-B783-427A-B5F9-8CBFC75A152E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9E09183-FFCB-49FF-B69E-8EC8B6B8DCD7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4658677F-DFAC-47A2-8C6E-7C4307640A24}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="373">
   <si>
     <t>Date</t>
   </si>
@@ -1016,6 +1016,160 @@
   </si>
   <si>
     <t>MAMEE PREMIUM NOODLES CURRY (1X5SX75G) *1</t>
+  </si>
+  <si>
+    <t>KING TO NIN JIOM PEI PA KOA 75ML *1</t>
+  </si>
+  <si>
+    <t>EA BABY CORN 100G (THA) P10</t>
+  </si>
+  <si>
+    <t>TY MUSHROOM - ENOKI 100G (THA) P50</t>
+  </si>
+  <si>
+    <t>BAWANG BESAR KUNING *1</t>
+  </si>
+  <si>
+    <t>HARUMI CHICKEN WHOLE LEG</t>
+  </si>
+  <si>
+    <t>GINGER- GALANGAL (LENGKUAS) 200G (MYS) P10</t>
+  </si>
+  <si>
+    <t>YK DAUN LIMAU PURUT 20G (MYS) P10</t>
+  </si>
+  <si>
+    <t>YK CORIANDER (KETUMBAR) 50G (MYS) P20</t>
+  </si>
+  <si>
+    <t>CHILI-PADI (KAMPUNG) (MYS)</t>
+  </si>
+  <si>
+    <t>MAE PRANOM INSTANT TOMYUM PASTE 114G *1</t>
+  </si>
+  <si>
+    <t>JOHN CRAFT KNIFE BLACK HANDLE 7IN 6047</t>
+  </si>
+  <si>
+    <t>METAL STRAINGER 20CM</t>
+  </si>
+  <si>
+    <t>Tomyam</t>
+  </si>
+  <si>
+    <t>HEINZ TOMATO KETCHUP 300G *1</t>
+  </si>
+  <si>
+    <t>ABC KICAP MANIS 132ML *1</t>
+  </si>
+  <si>
+    <t>BAWANG PUTIH *1</t>
+  </si>
+  <si>
+    <t>MUSHROOM-ENOKI 100GM (MYS) P50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In order
+letak 
+air (sampai panas)
+lengkuas
+serai
+daun limau purut
+daun ketumbar (then wait for 5 minutes)
+and then letak ayam
+letak kiub ayam
+letak sos ikan
+letak sos tiram
+tomyam paste
+garam
+bawang holland
+kobis bunga
+mushroom
+ </t>
+  </si>
+  <si>
+    <t>KNORR CHICKEN CUBES NO MSG(6S) 60G</t>
+  </si>
+  <si>
+    <t>CUCUMBER - JAPANESE (KYURI) (MYS) K10</t>
+  </si>
+  <si>
+    <t>Ayam Rempah part 2</t>
+  </si>
+  <si>
+    <t>Crispy chicken</t>
+  </si>
+  <si>
+    <t>Basuh ayam</t>
+  </si>
+  <si>
+    <t>cucuk ayam guna garpu</t>
+  </si>
+  <si>
+    <t>letak garam as marinate</t>
+  </si>
+  <si>
+    <t>letak baking soda</t>
+  </si>
+  <si>
+    <t>letak air</t>
+  </si>
+  <si>
+    <t>letak 2 dua telur</t>
+  </si>
+  <si>
+    <t>SUNGLO LASSI APPLE 700ML *1</t>
+  </si>
+  <si>
+    <t>KBL CHILLI SAUCE 500G *1</t>
+  </si>
+  <si>
+    <t>NUTRIPLUS ORGANIC SELENIUM EGG (10S) *1</t>
+  </si>
+  <si>
+    <t>LONG BEAN (KACANG PANJANG) (MYS)</t>
+  </si>
+  <si>
+    <t>PUTERI CHILLI GILING (3 IN 1) 200G *1</t>
+  </si>
+  <si>
+    <t>YK CHILI-PADI RED 100G (THA) P40</t>
+  </si>
+  <si>
+    <t>CAPSICUM-RED (MYS) K5</t>
+  </si>
+  <si>
+    <t>BANANA-HS LAKATAN BERANGAN (MYS) K15</t>
+  </si>
+  <si>
+    <t>CG PROBIOTIC SIEW PAK CHOY 250G (MYS)P20</t>
+  </si>
+  <si>
+    <t>FACE TOWEL-DARK PLAIN 12X12IN 40G 2209</t>
+  </si>
+  <si>
+    <t>GVC A/B SHOWER CREAM - L&amp;W/M-REFILL 550G</t>
+  </si>
+  <si>
+    <t>SUNWHITE BERAS WANGI 1KG *1</t>
+  </si>
+  <si>
+    <t>SEASONS CHRYSANTHENUM TEA 1LIT *1</t>
+  </si>
+  <si>
+    <t>Spaghetti with chicken</t>
+  </si>
+  <si>
+    <t>MARINA TEMPURA CHICKEN NUGGET 750G</t>
+  </si>
+  <si>
+    <t>NUTRIPLUS ORGANIC SELENIUM EGG  (10S) *1</t>
+  </si>
+  <si>
+    <t>SEKOPLAS ENVIROPLUS GARBAGE ROLL -M (68X84CMX20S) GN</t>
+  </si>
+  <si>
+    <t>GAREDNIA ORIGINAL CLASSIC JUMBO 600 *1</t>
   </si>
 </sst>
 </file>
@@ -1130,7 +1284,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1163,6 +1317,19 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1193,8 +1360,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CF63E7CD-18A2-4918-AE48-6D9DD5DB55B7}" name="Table1" displayName="Table1" ref="A1:D579" totalsRowShown="0">
-  <autoFilter ref="A1:D579" xr:uid="{CF63E7CD-18A2-4918-AE48-6D9DD5DB55B7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CF63E7CD-18A2-4918-AE48-6D9DD5DB55B7}" name="Table1" displayName="Table1" ref="A1:D657" totalsRowShown="0">
+  <autoFilter ref="A1:D657" xr:uid="{CF63E7CD-18A2-4918-AE48-6D9DD5DB55B7}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{3FF5C65C-C3A8-4E20-8338-7D6593C60B8B}" name="Date" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{E2DBD41B-ADF3-48D8-839D-9E340056EB1F}" name="Grocery Item"/>
@@ -1502,7 +1669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F1FE89E-F524-4366-B417-1C841F4683A9}">
-  <dimension ref="A1:D579"/>
+  <dimension ref="A1:D657"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -9614,6 +9781,1098 @@
         <v>3</v>
       </c>
       <c r="D579" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A580" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B580" t="s">
+        <v>327</v>
+      </c>
+      <c r="C580" s="2">
+        <v>10.25</v>
+      </c>
+      <c r="D580" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A581" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B581" t="s">
+        <v>88</v>
+      </c>
+      <c r="C581" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="D581" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A582" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B582" t="s">
+        <v>306</v>
+      </c>
+      <c r="C582" s="2">
+        <v>5.45</v>
+      </c>
+      <c r="D582" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A583" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B583" t="s">
+        <v>106</v>
+      </c>
+      <c r="C583" s="2">
+        <v>2.93</v>
+      </c>
+      <c r="D583" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A584" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B584" t="s">
+        <v>328</v>
+      </c>
+      <c r="C584" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="D584" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A585" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B585" t="s">
+        <v>329</v>
+      </c>
+      <c r="C585" s="2">
+        <v>1</v>
+      </c>
+      <c r="D585" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A586" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B586" t="s">
+        <v>244</v>
+      </c>
+      <c r="C586" s="2">
+        <v>1.46</v>
+      </c>
+      <c r="D586" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A587" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B587" t="s">
+        <v>330</v>
+      </c>
+      <c r="C587" s="2">
+        <v>0.62</v>
+      </c>
+      <c r="D587" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A588" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B588" t="s">
+        <v>179</v>
+      </c>
+      <c r="C588" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="D588" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A589" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B589" t="s">
+        <v>331</v>
+      </c>
+      <c r="C589" s="2">
+        <v>7.72</v>
+      </c>
+      <c r="D589" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A590" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B590" t="s">
+        <v>292</v>
+      </c>
+      <c r="C590" s="2">
+        <v>5.83</v>
+      </c>
+      <c r="D590" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A591" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B591" t="s">
+        <v>332</v>
+      </c>
+      <c r="C591" s="2">
+        <v>3</v>
+      </c>
+      <c r="D591" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A592" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B592" t="s">
+        <v>333</v>
+      </c>
+      <c r="C592" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D592" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A593" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B593" t="s">
+        <v>334</v>
+      </c>
+      <c r="C593" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="D593" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A594" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B594" t="s">
+        <v>335</v>
+      </c>
+      <c r="C594" s="2">
+        <v>1.73</v>
+      </c>
+      <c r="D594" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A595" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B595" t="s">
+        <v>336</v>
+      </c>
+      <c r="C595" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="D595" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A596" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B596" t="s">
+        <v>337</v>
+      </c>
+      <c r="C596" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="D596" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A597" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B597" t="s">
+        <v>338</v>
+      </c>
+      <c r="C597" s="2">
+        <v>15.4</v>
+      </c>
+      <c r="D597" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A598" s="1">
+        <v>45823</v>
+      </c>
+      <c r="B598" t="s">
+        <v>225</v>
+      </c>
+      <c r="C598" s="2">
+        <v>12.7</v>
+      </c>
+      <c r="D598" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A599" s="1">
+        <v>45823</v>
+      </c>
+      <c r="B599" t="s">
+        <v>116</v>
+      </c>
+      <c r="C599" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="D599" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A600" s="1">
+        <v>45823</v>
+      </c>
+      <c r="B600" t="s">
+        <v>272</v>
+      </c>
+      <c r="C600" s="2">
+        <v>8.15</v>
+      </c>
+      <c r="D600" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A601" s="1">
+        <v>45823</v>
+      </c>
+      <c r="B601" t="s">
+        <v>340</v>
+      </c>
+      <c r="C601" s="2">
+        <v>5.49</v>
+      </c>
+      <c r="D601" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A602" s="1">
+        <v>45823</v>
+      </c>
+      <c r="B602" t="s">
+        <v>341</v>
+      </c>
+      <c r="C602" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="D602" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A603" s="1">
+        <v>45823</v>
+      </c>
+      <c r="B603" t="s">
+        <v>244</v>
+      </c>
+      <c r="C603" s="2">
+        <v>0.94</v>
+      </c>
+      <c r="D603" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A604" s="1">
+        <v>45823</v>
+      </c>
+      <c r="B604" t="s">
+        <v>342</v>
+      </c>
+      <c r="C604" s="2">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="D604" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A605" s="1">
+        <v>45823</v>
+      </c>
+      <c r="B605" t="s">
+        <v>328</v>
+      </c>
+      <c r="C605" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="D605" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A606" s="1">
+        <v>45823</v>
+      </c>
+      <c r="B606" t="s">
+        <v>343</v>
+      </c>
+      <c r="C606" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="D606" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A607" s="1">
+        <v>45823</v>
+      </c>
+      <c r="B607" t="s">
+        <v>212</v>
+      </c>
+      <c r="C607" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="D607" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A608" s="1">
+        <v>45827</v>
+      </c>
+      <c r="B608" t="s">
+        <v>272</v>
+      </c>
+      <c r="C608" s="2">
+        <v>8.94</v>
+      </c>
+      <c r="D608" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A609" s="1">
+        <v>45827</v>
+      </c>
+      <c r="B609" t="s">
+        <v>290</v>
+      </c>
+      <c r="C609" s="2">
+        <v>2.65</v>
+      </c>
+      <c r="D609" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A610" s="1">
+        <v>45827</v>
+      </c>
+      <c r="B610" t="s">
+        <v>290</v>
+      </c>
+      <c r="C610" s="2">
+        <v>2.65</v>
+      </c>
+      <c r="D610" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A611" s="1">
+        <v>45827</v>
+      </c>
+      <c r="B611" t="s">
+        <v>345</v>
+      </c>
+      <c r="C611" s="2">
+        <v>3.95</v>
+      </c>
+      <c r="D611" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A612" s="1">
+        <v>45827</v>
+      </c>
+      <c r="B612" t="s">
+        <v>131</v>
+      </c>
+      <c r="C612" s="2">
+        <v>4.42</v>
+      </c>
+      <c r="D612" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A613" s="1">
+        <v>45827</v>
+      </c>
+      <c r="B613" t="s">
+        <v>346</v>
+      </c>
+      <c r="C613" s="2">
+        <v>2.65</v>
+      </c>
+      <c r="D613" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A614" s="1">
+        <v>45830</v>
+      </c>
+      <c r="B614" t="s">
+        <v>355</v>
+      </c>
+      <c r="C614" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="D614" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A615" s="1">
+        <v>45830</v>
+      </c>
+      <c r="B615" t="s">
+        <v>356</v>
+      </c>
+      <c r="C615" s="2">
+        <v>5.95</v>
+      </c>
+      <c r="D615" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A616" s="1">
+        <v>45830</v>
+      </c>
+      <c r="B616" t="s">
+        <v>272</v>
+      </c>
+      <c r="C616" s="2">
+        <v>10.210000000000001</v>
+      </c>
+      <c r="D616" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A617" s="1">
+        <v>45830</v>
+      </c>
+      <c r="B617" t="s">
+        <v>357</v>
+      </c>
+      <c r="C617" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="D617" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A618" s="1">
+        <v>45830</v>
+      </c>
+      <c r="B618" t="s">
+        <v>328</v>
+      </c>
+      <c r="C618" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="D618" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A619" s="1">
+        <v>45830</v>
+      </c>
+      <c r="B619" t="s">
+        <v>106</v>
+      </c>
+      <c r="C619" s="2">
+        <v>2.71</v>
+      </c>
+      <c r="D619" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A620" s="1">
+        <v>45830</v>
+      </c>
+      <c r="B620" t="s">
+        <v>333</v>
+      </c>
+      <c r="C620" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D620" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A621" s="1">
+        <v>45830</v>
+      </c>
+      <c r="B621" t="s">
+        <v>358</v>
+      </c>
+      <c r="C621" s="2">
+        <v>3.32</v>
+      </c>
+      <c r="D621" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A622" s="1">
+        <v>45830</v>
+      </c>
+      <c r="B622" t="s">
+        <v>359</v>
+      </c>
+      <c r="C622" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="D622" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A623" s="1">
+        <v>45830</v>
+      </c>
+      <c r="B623" t="s">
+        <v>360</v>
+      </c>
+      <c r="C623" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D623" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A624" s="1">
+        <v>45830</v>
+      </c>
+      <c r="B624" t="s">
+        <v>361</v>
+      </c>
+      <c r="C624" s="2">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="D624" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A625" s="1">
+        <v>45830</v>
+      </c>
+      <c r="B625" t="s">
+        <v>330</v>
+      </c>
+      <c r="C625" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="D625" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A626" s="1">
+        <v>45830</v>
+      </c>
+      <c r="B626" t="s">
+        <v>362</v>
+      </c>
+      <c r="C626" s="2">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="D626" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A627" s="1">
+        <v>45830</v>
+      </c>
+      <c r="B627" t="s">
+        <v>212</v>
+      </c>
+      <c r="C627" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="D627" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A628" s="1">
+        <v>45836</v>
+      </c>
+      <c r="B628" t="s">
+        <v>323</v>
+      </c>
+      <c r="C628" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="D628" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A629" s="1">
+        <v>45836</v>
+      </c>
+      <c r="B629" t="s">
+        <v>363</v>
+      </c>
+      <c r="C629" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="D629" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A630" s="1">
+        <v>45836</v>
+      </c>
+      <c r="B630" t="s">
+        <v>170</v>
+      </c>
+      <c r="C630" s="2">
+        <v>3</v>
+      </c>
+      <c r="D630" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A631" s="1">
+        <v>45836</v>
+      </c>
+      <c r="B631" t="s">
+        <v>328</v>
+      </c>
+      <c r="C631" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="D631" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A632" s="1">
+        <v>45836</v>
+      </c>
+      <c r="B632" t="s">
+        <v>329</v>
+      </c>
+      <c r="C632" s="2">
+        <v>1</v>
+      </c>
+      <c r="D632" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A633" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B633" t="s">
+        <v>306</v>
+      </c>
+      <c r="C633" s="2">
+        <v>5.45</v>
+      </c>
+      <c r="D633" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A634" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B634" t="s">
+        <v>211</v>
+      </c>
+      <c r="C634" s="2">
+        <v>9.3800000000000008</v>
+      </c>
+      <c r="D634" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A635" s="1">
+        <v>45840</v>
+      </c>
+      <c r="B635" t="s">
+        <v>212</v>
+      </c>
+      <c r="C635" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="D635" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A636" s="1">
+        <v>45840</v>
+      </c>
+      <c r="B636" t="s">
+        <v>357</v>
+      </c>
+      <c r="C636" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="D636" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A637" s="1">
+        <v>45840</v>
+      </c>
+      <c r="B637" t="s">
+        <v>364</v>
+      </c>
+      <c r="C637" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D637" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A638" s="1">
+        <v>45840</v>
+      </c>
+      <c r="B638" t="s">
+        <v>364</v>
+      </c>
+      <c r="C638" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D638" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A639" s="1">
+        <v>45842</v>
+      </c>
+      <c r="B639" t="s">
+        <v>112</v>
+      </c>
+      <c r="C639" s="2">
+        <v>8.76</v>
+      </c>
+      <c r="D639" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A640" s="1">
+        <v>45842</v>
+      </c>
+      <c r="B640" t="s">
+        <v>211</v>
+      </c>
+      <c r="C640" s="2">
+        <v>9.17</v>
+      </c>
+      <c r="D640" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A641" s="1">
+        <v>45842</v>
+      </c>
+      <c r="B641" t="s">
+        <v>244</v>
+      </c>
+      <c r="C641" s="2">
+        <v>2.57</v>
+      </c>
+      <c r="D641" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A642" s="1">
+        <v>45840</v>
+      </c>
+      <c r="B642" t="s">
+        <v>365</v>
+      </c>
+      <c r="C642" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="D642" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A643" s="1">
+        <v>45847</v>
+      </c>
+      <c r="B643" t="s">
+        <v>212</v>
+      </c>
+      <c r="C643" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="D643" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A644" s="1">
+        <v>45847</v>
+      </c>
+      <c r="B644" t="s">
+        <v>357</v>
+      </c>
+      <c r="C644" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="D644" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A645" s="1">
+        <v>45851</v>
+      </c>
+      <c r="B645" t="s">
+        <v>366</v>
+      </c>
+      <c r="C645" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="D645" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A646" s="1">
+        <v>45851</v>
+      </c>
+      <c r="B646" t="s">
+        <v>367</v>
+      </c>
+      <c r="C646" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="D646" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A647" s="1">
+        <v>45851</v>
+      </c>
+      <c r="B647" t="s">
+        <v>346</v>
+      </c>
+      <c r="C647" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="D647" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A648" s="1">
+        <v>45851</v>
+      </c>
+      <c r="B648" t="s">
+        <v>306</v>
+      </c>
+      <c r="C648" s="2">
+        <v>5.45</v>
+      </c>
+      <c r="D648" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A649" s="1">
+        <v>45858</v>
+      </c>
+      <c r="B649" t="s">
+        <v>146</v>
+      </c>
+      <c r="C649" s="2">
+        <v>12.7</v>
+      </c>
+      <c r="D649" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A650" s="1">
+        <v>45858</v>
+      </c>
+      <c r="B650" t="s">
+        <v>323</v>
+      </c>
+      <c r="C650" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="D650" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A651" s="1">
+        <v>45858</v>
+      </c>
+      <c r="B651" t="s">
+        <v>369</v>
+      </c>
+      <c r="C651" s="2">
+        <v>16.7</v>
+      </c>
+      <c r="D651" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A652" s="1">
+        <v>45858</v>
+      </c>
+      <c r="B652" t="s">
+        <v>370</v>
+      </c>
+      <c r="C652" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="D652" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A653" s="1">
+        <v>45858</v>
+      </c>
+      <c r="B653" t="s">
+        <v>290</v>
+      </c>
+      <c r="C653" s="2">
+        <v>2.65</v>
+      </c>
+      <c r="D653" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A654" s="1">
+        <v>45858</v>
+      </c>
+      <c r="B654" t="s">
+        <v>367</v>
+      </c>
+      <c r="C654" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="D654" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A655" s="1">
+        <v>45858</v>
+      </c>
+      <c r="B655" t="s">
+        <v>371</v>
+      </c>
+      <c r="C655" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="D655" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A656" s="1">
+        <v>45858</v>
+      </c>
+      <c r="B656" t="s">
+        <v>306</v>
+      </c>
+      <c r="C656" s="2">
+        <v>5.45</v>
+      </c>
+      <c r="D656" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A657" s="1">
+        <v>45858</v>
+      </c>
+      <c r="B657" t="s">
+        <v>372</v>
+      </c>
+      <c r="C657" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="D657" t="s">
         <v>22</v>
       </c>
     </row>
@@ -9629,7 +10888,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47AC92D9-8D81-4D6D-9D00-CF5410D2E104}">
-  <dimension ref="A2:I65"/>
+  <dimension ref="A2:I100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" customWidth="1"/>
@@ -9894,6 +11153,9 @@
         <v>203</v>
       </c>
       <c r="C21" s="14"/>
+      <c r="G21" s="12" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
@@ -9902,6 +11164,12 @@
       <c r="C22" s="16">
         <v>2.71</v>
       </c>
+      <c r="G22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H22" s="8">
+        <v>2.21</v>
+      </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
@@ -9910,6 +11178,12 @@
       <c r="C23" s="16">
         <v>4.53</v>
       </c>
+      <c r="G23" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="H23" s="19">
+        <v>11.57</v>
+      </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
@@ -9918,6 +11192,12 @@
       <c r="C24" s="16">
         <v>4.9000000000000004</v>
       </c>
+      <c r="G24" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H24" s="10">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
@@ -9926,6 +11206,12 @@
       <c r="C25" s="16">
         <v>3.9</v>
       </c>
+      <c r="G25" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="H25" s="10">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
@@ -9933,6 +11219,12 @@
       </c>
       <c r="C26" s="16">
         <v>11.66</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="H26" s="10">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
@@ -9944,263 +11236,511 @@
         <f>27.7/3</f>
         <v>9.2333333333333325</v>
       </c>
+      <c r="H27" s="11">
+        <f>SUM(H22:H26)</f>
+        <v>27.98</v>
+      </c>
+      <c r="I27">
+        <f>27.98/3</f>
+        <v>9.3266666666666662</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="C29" s="14"/>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C30" s="8">
+        <v>8.94</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B31" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" s="8">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B32" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C32" s="10">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C33" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C34" s="11">
+        <f>SUM(C30:C33)</f>
+        <v>20.909999999999997</v>
+      </c>
+      <c r="D34">
+        <f>20.91/3</f>
+        <v>6.97</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="C30" s="14"/>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="14" t="s">
+      <c r="C36" s="14"/>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C37" s="17">
         <v>5.9</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="14" t="s">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="C32" s="17">
+      <c r="C38" s="17">
         <v>5.3</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B36" s="12" t="s">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B42" s="12" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B37" s="15" t="s">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B43" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C37" s="16">
+      <c r="C43" s="16">
         <v>4.6900000000000004</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B38" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="C38" s="16">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B39" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="C39" s="17">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B40" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="C40" s="16">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B41" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="C41" s="17">
-        <v>9.3000000000000007</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B42" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="C42" s="16">
-        <v>0.94</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B43" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="C43" s="17">
-        <v>1.2</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="C44" s="16">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="C45" s="17">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C46" s="16">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="C47" s="17">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B48" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" s="16">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="C49" s="17">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="C44" s="16">
+      <c r="C50" s="16">
         <v>0.31</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B45" s="15" t="s">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B51" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C45" s="16">
+      <c r="C51" s="16">
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="11">
-        <f>SUM(C37:C45)</f>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C52" s="11">
+        <f>SUM(C43:C51)</f>
         <v>34.500000000000007</v>
       </c>
-      <c r="D46">
+      <c r="D52">
         <f>34.5/3</f>
         <v>11.5</v>
       </c>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B48" s="12" t="s">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54" s="12" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="3" t="s">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B55" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C49" s="8">
+      <c r="C55" s="8">
         <v>5.3</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B50" s="5" t="s">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B56" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="C50" s="10">
+      <c r="C56" s="10">
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B51" s="3" t="s">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B57" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="C51" s="8">
+      <c r="C57" s="8">
         <v>7.8</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B52" s="5" t="s">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B58" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="C52" s="10">
+      <c r="C58" s="10">
         <v>4.7</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B53" s="5" t="s">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B59" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="C53" s="10">
+      <c r="C59" s="10">
         <v>3.59</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B54" s="3" t="s">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B60" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C54" s="8">
+      <c r="C60" s="8">
         <v>8.4</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C55" s="11">
-        <f>SUM(C49:C54)</f>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C61" s="11">
+        <f>SUM(C55:C60)</f>
         <v>38.99</v>
       </c>
-      <c r="D55">
+      <c r="D61">
         <v>32.99</v>
       </c>
-      <c r="E55">
+      <c r="E61">
         <f>32.99/3</f>
         <v>10.996666666666668</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B57" s="5" t="s">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B63" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="C57" s="10"/>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B58" s="3" t="s">
+      <c r="C63" s="22"/>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B64" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C58" s="8">
+      <c r="C64" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B59" s="5" t="s">
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B65" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="C59" s="10">
+      <c r="C65" s="10">
         <v>4.8099999999999996</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B60" s="5" t="s">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B66" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C60" s="10">
+      <c r="C66" s="10">
         <v>2.66</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B61" s="5" t="s">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B67" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C61" s="10">
+      <c r="C67" s="10">
         <v>0.62</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B62" s="3" t="s">
+    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B68" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C62" s="8">
+      <c r="C68" s="8">
         <v>36.82</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B63" s="3" t="s">
+    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B69" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C63" s="8">
+      <c r="C69" s="8">
         <v>1.05</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B64" s="5" t="s">
+    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B70" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="C64" s="10">
+      <c r="C70" s="10">
         <v>2.5</v>
       </c>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C65" s="11">
-        <f>SUM(C58:C64)</f>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C71" s="11">
+        <f>SUM(C64:C70)</f>
         <v>51.459999999999994</v>
       </c>
-      <c r="D65">
+      <c r="D71">
         <f>51.46/7</f>
         <v>7.3514285714285714</v>
       </c>
     </row>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B73" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="C73" s="12"/>
+    </row>
+    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B74" s="5"/>
+      <c r="C74" s="10"/>
+      <c r="G74" s="24" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="C75" s="10">
+        <v>2.93</v>
+      </c>
+      <c r="G75" s="24"/>
+    </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B76" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C76" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="G76" s="24"/>
+    </row>
+    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B77" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C77" s="10">
+        <v>1</v>
+      </c>
+      <c r="G77" s="24"/>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C78" s="8">
+        <v>1.46</v>
+      </c>
+      <c r="G78" s="24"/>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B79" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C79" s="10">
+        <v>0.62</v>
+      </c>
+      <c r="G79" s="24"/>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B80" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C80" s="8">
+        <v>0.39</v>
+      </c>
+      <c r="G80" s="24"/>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B81" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="C81" s="10">
+        <v>7.72</v>
+      </c>
+      <c r="G81" s="24"/>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B82" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C82" s="8">
+        <v>5.83</v>
+      </c>
+      <c r="G82" s="24"/>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B83" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="C83" s="10">
+        <v>3</v>
+      </c>
+      <c r="G83" s="24"/>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B84" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C84" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G84" s="24"/>
+    </row>
+    <row r="85" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B85" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="C85" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="G85" s="24"/>
+    </row>
+    <row r="86" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B86" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C86" s="8">
+        <v>1.73</v>
+      </c>
+      <c r="G86" s="24"/>
+    </row>
+    <row r="87" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B87" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="C87" s="10">
+        <v>6.2</v>
+      </c>
+      <c r="G87" s="24"/>
+    </row>
+    <row r="88" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C88" s="11">
+        <f>SUM(C74:C87)</f>
+        <v>37.680000000000007</v>
+      </c>
+      <c r="D88">
+        <f>37.68/4</f>
+        <v>9.42</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G91" s="23" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G92" s="23" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G93" s="23" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G94" s="23" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G95" s="23"/>
+    </row>
+    <row r="96" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G96" s="23"/>
+    </row>
+    <row r="97" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G97" s="23" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="98" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G98" s="23" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="99" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G99" s="23" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="100" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G100" s="23"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G74:G87"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Groceries.xlsx
+++ b/Groceries.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a960143ed076ae3/Desktop/Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2739" documentId="8_{98EF138E-B783-427A-B5F9-8CBFC75A152E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9E09183-FFCB-49FF-B69E-8EC8B6B8DCD7}"/>
+  <xr:revisionPtr revIDLastSave="3066" documentId="8_{98EF138E-B783-427A-B5F9-8CBFC75A152E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55273673-A45B-45C0-816D-550EEEA274E9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4658677F-DFAC-47A2-8C6E-7C4307640A24}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="ayam" sheetId="2" r:id="rId2"/>
+    <sheet name="Recipe" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="397">
   <si>
     <t>Date</t>
   </si>
@@ -1170,6 +1170,78 @@
   </si>
   <si>
     <t>GAREDNIA ORIGINAL CLASSIC JUMBO 600 *1</t>
+  </si>
+  <si>
+    <t>SAN REMO INSTANT LASAGNA 250G *1</t>
+  </si>
+  <si>
+    <t>PREGO MUSHROOM PASTE SAUCE 350G *1</t>
+  </si>
+  <si>
+    <t>MUSHROOM-BUNA SHIMEIJI 150 (CHN)P40</t>
+  </si>
+  <si>
+    <t>HARUMI CHICKEN RIBS</t>
+  </si>
+  <si>
+    <t>FAMILY PIZZA TOPPING MO/SHREDDED 150G *1</t>
+  </si>
+  <si>
+    <t>TAE PEI BAWANG GORENG 100G *1</t>
+  </si>
+  <si>
+    <t>CG PROBIOTIC LEAF CELERY (DAUN SUP) 100G</t>
+  </si>
+  <si>
+    <t>MERIAH WHITE PEPPER POWDER 60G</t>
+  </si>
+  <si>
+    <t>COLGATE TOTAL SENSITIVITY &amp; GUM 110G</t>
+  </si>
+  <si>
+    <t>BAWANG KECIL *1</t>
+  </si>
+  <si>
+    <t>LIFE TOMATO SAUCE 485G *1</t>
+  </si>
+  <si>
+    <t>7 UP 1.5LIT *1</t>
+  </si>
+  <si>
+    <t>OLD GINGER BENTONG (HALIA TUA BENTONG)</t>
+  </si>
+  <si>
+    <t>YK SIEW  PAK CHOY 250G (MYS) P10</t>
+  </si>
+  <si>
+    <t>DMB BELACAN BAKAR 20G *1</t>
+  </si>
+  <si>
+    <t>DL UHT MILK LOW FAT 6X200ML *1</t>
+  </si>
+  <si>
+    <t>CHEK HUP MICROGROUND MATCHA LATTE 6X23G</t>
+  </si>
+  <si>
+    <t>NESTLE KIT KAT HOT CHOCOLATE PREMIX 10X33G</t>
+  </si>
+  <si>
+    <t>MUSHROOM-WHITE BUTTON SLICES 125G P20</t>
+  </si>
+  <si>
+    <t>MISSION TORTILLA ONION &amp; CHIVE 360GM *1</t>
+  </si>
+  <si>
+    <t>PREGO MUSHROOM PASTE SAUCE 680G *1</t>
+  </si>
+  <si>
+    <t>LABOUR PASTE DISHWAS (LIME) 750G *1</t>
+  </si>
+  <si>
+    <t>Pizza Wraps</t>
+  </si>
+  <si>
+    <t>ZUS SIGN MIXES COFFEE - DOLCE LATTE</t>
   </si>
 </sst>
 </file>
@@ -1360,8 +1432,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CF63E7CD-18A2-4918-AE48-6D9DD5DB55B7}" name="Table1" displayName="Table1" ref="A1:D657" totalsRowShown="0">
-  <autoFilter ref="A1:D657" xr:uid="{CF63E7CD-18A2-4918-AE48-6D9DD5DB55B7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CF63E7CD-18A2-4918-AE48-6D9DD5DB55B7}" name="Table1" displayName="Table1" ref="A1:D726" totalsRowShown="0">
+  <autoFilter ref="A1:D726" xr:uid="{CF63E7CD-18A2-4918-AE48-6D9DD5DB55B7}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{3FF5C65C-C3A8-4E20-8338-7D6593C60B8B}" name="Date" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{E2DBD41B-ADF3-48D8-839D-9E340056EB1F}" name="Grocery Item"/>
@@ -1669,7 +1741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F1FE89E-F524-4366-B417-1C841F4683A9}">
-  <dimension ref="A1:D657"/>
+  <dimension ref="A1:D726"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -10752,13 +10824,13 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A649" s="1">
-        <v>45858</v>
+        <v>45855</v>
       </c>
       <c r="B649" t="s">
-        <v>146</v>
+        <v>300</v>
       </c>
       <c r="C649" s="2">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="D649" t="s">
         <v>22</v>
@@ -10766,13 +10838,13 @@
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" s="1">
-        <v>45858</v>
+        <v>45855</v>
       </c>
       <c r="B650" t="s">
-        <v>323</v>
+        <v>378</v>
       </c>
       <c r="C650" s="2">
-        <v>5.2</v>
+        <v>2.85</v>
       </c>
       <c r="D650" t="s">
         <v>22</v>
@@ -10780,13 +10852,13 @@
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A651" s="1">
-        <v>45858</v>
+        <v>45855</v>
       </c>
       <c r="B651" t="s">
-        <v>369</v>
+        <v>211</v>
       </c>
       <c r="C651" s="2">
-        <v>16.7</v>
+        <v>7.21</v>
       </c>
       <c r="D651" t="s">
         <v>22</v>
@@ -10794,13 +10866,13 @@
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A652" s="1">
-        <v>45858</v>
+        <v>45855</v>
       </c>
       <c r="B652" t="s">
-        <v>370</v>
+        <v>208</v>
       </c>
       <c r="C652" s="2">
-        <v>7.9</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="D652" t="s">
         <v>22</v>
@@ -10808,13 +10880,13 @@
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A653" s="1">
-        <v>45858</v>
+        <v>45855</v>
       </c>
       <c r="B653" t="s">
-        <v>290</v>
+        <v>76</v>
       </c>
       <c r="C653" s="2">
-        <v>2.65</v>
+        <v>0.88</v>
       </c>
       <c r="D653" t="s">
         <v>22</v>
@@ -10822,13 +10894,13 @@
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A654" s="1">
-        <v>45858</v>
+        <v>45855</v>
       </c>
       <c r="B654" t="s">
-        <v>367</v>
+        <v>131</v>
       </c>
       <c r="C654" s="2">
-        <v>2.9</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="D654" t="s">
         <v>22</v>
@@ -10836,13 +10908,13 @@
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A655" s="1">
-        <v>45858</v>
+        <v>45855</v>
       </c>
       <c r="B655" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C655" s="2">
-        <v>6.8</v>
+        <v>1.9</v>
       </c>
       <c r="D655" t="s">
         <v>22</v>
@@ -10850,13 +10922,13 @@
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A656" s="1">
-        <v>45858</v>
+        <v>45855</v>
       </c>
       <c r="B656" t="s">
-        <v>306</v>
+        <v>106</v>
       </c>
       <c r="C656" s="2">
-        <v>5.45</v>
+        <v>1.9</v>
       </c>
       <c r="D656" t="s">
         <v>22</v>
@@ -10864,15 +10936,981 @@
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A657" s="1">
+        <v>45855</v>
+      </c>
+      <c r="B657" t="s">
+        <v>380</v>
+      </c>
+      <c r="C657" s="2">
+        <v>6.4</v>
+      </c>
+      <c r="D657" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A658" s="1">
         <v>45858</v>
       </c>
-      <c r="B657" t="s">
+      <c r="B658" t="s">
+        <v>146</v>
+      </c>
+      <c r="C658" s="2">
+        <v>12.7</v>
+      </c>
+      <c r="D658" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A659" s="1">
+        <v>45858</v>
+      </c>
+      <c r="B659" t="s">
+        <v>323</v>
+      </c>
+      <c r="C659" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="D659" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A660" s="1">
+        <v>45858</v>
+      </c>
+      <c r="B660" t="s">
+        <v>369</v>
+      </c>
+      <c r="C660" s="2">
+        <v>16.7</v>
+      </c>
+      <c r="D660" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A661" s="1">
+        <v>45858</v>
+      </c>
+      <c r="B661" t="s">
+        <v>370</v>
+      </c>
+      <c r="C661" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="D661" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A662" s="1">
+        <v>45858</v>
+      </c>
+      <c r="B662" t="s">
+        <v>290</v>
+      </c>
+      <c r="C662" s="2">
+        <v>2.65</v>
+      </c>
+      <c r="D662" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A663" s="1">
+        <v>45858</v>
+      </c>
+      <c r="B663" t="s">
+        <v>367</v>
+      </c>
+      <c r="C663" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="D663" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A664" s="1">
+        <v>45858</v>
+      </c>
+      <c r="B664" t="s">
+        <v>371</v>
+      </c>
+      <c r="C664" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="D664" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A665" s="1">
+        <v>45858</v>
+      </c>
+      <c r="B665" t="s">
+        <v>306</v>
+      </c>
+      <c r="C665" s="2">
+        <v>5.45</v>
+      </c>
+      <c r="D665" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A666" s="1">
+        <v>45858</v>
+      </c>
+      <c r="B666" t="s">
         <v>372</v>
       </c>
-      <c r="C657" s="2">
+      <c r="C666" s="2">
         <v>4.3</v>
       </c>
-      <c r="D657" t="s">
+      <c r="D666" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A667" s="1">
+        <v>45867</v>
+      </c>
+      <c r="B667" t="s">
+        <v>342</v>
+      </c>
+      <c r="C667" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="D667" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A668" s="1">
+        <v>45867</v>
+      </c>
+      <c r="B668" t="s">
+        <v>330</v>
+      </c>
+      <c r="C668" s="2">
+        <v>0.78</v>
+      </c>
+      <c r="D668" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A669" s="1">
+        <v>45867</v>
+      </c>
+      <c r="B669" t="s">
+        <v>373</v>
+      </c>
+      <c r="C669" s="2">
+        <v>5.95</v>
+      </c>
+      <c r="D669" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A670" s="1">
+        <v>45867</v>
+      </c>
+      <c r="B670" t="s">
+        <v>374</v>
+      </c>
+      <c r="C670" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="D670" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A671" s="1">
+        <v>45867</v>
+      </c>
+      <c r="B671" t="s">
+        <v>375</v>
+      </c>
+      <c r="C671" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="D671" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A672" s="1">
+        <v>45867</v>
+      </c>
+      <c r="B672" t="s">
+        <v>376</v>
+      </c>
+      <c r="C672" s="2">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="D672" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A673" s="1">
+        <v>45867</v>
+      </c>
+      <c r="B673" t="s">
+        <v>377</v>
+      </c>
+      <c r="C673" s="2">
+        <v>13.95</v>
+      </c>
+      <c r="D673" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A674" s="1">
+        <v>45867</v>
+      </c>
+      <c r="B674" t="s">
+        <v>306</v>
+      </c>
+      <c r="C674" s="2">
+        <v>5.45</v>
+      </c>
+      <c r="D674" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A675" s="1">
+        <v>45869</v>
+      </c>
+      <c r="B675" t="s">
+        <v>88</v>
+      </c>
+      <c r="C675" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="D675" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A676" s="1">
+        <v>45869</v>
+      </c>
+      <c r="B676" t="s">
+        <v>211</v>
+      </c>
+      <c r="C676" s="2">
+        <v>8.89</v>
+      </c>
+      <c r="D676" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A677" s="1">
+        <v>45869</v>
+      </c>
+      <c r="B677" t="s">
+        <v>244</v>
+      </c>
+      <c r="C677" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="D677" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A678" s="1">
+        <v>45872</v>
+      </c>
+      <c r="B678" t="s">
+        <v>212</v>
+      </c>
+      <c r="C678" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="D678" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A679" s="1">
+        <v>45872</v>
+      </c>
+      <c r="B679" t="s">
+        <v>323</v>
+      </c>
+      <c r="C679" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="D679" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A680" s="1">
+        <v>45872</v>
+      </c>
+      <c r="B680" t="s">
+        <v>381</v>
+      </c>
+      <c r="C680" s="2">
+        <v>15.49</v>
+      </c>
+      <c r="D680" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A681" s="1">
+        <v>45872</v>
+      </c>
+      <c r="B681" t="s">
+        <v>367</v>
+      </c>
+      <c r="C681" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="D681" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A682" s="1">
+        <v>45872</v>
+      </c>
+      <c r="B682" t="s">
+        <v>306</v>
+      </c>
+      <c r="C682" s="2">
+        <v>5.45</v>
+      </c>
+      <c r="D682" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A683" s="1">
+        <v>45872</v>
+      </c>
+      <c r="B683" t="s">
+        <v>357</v>
+      </c>
+      <c r="C683" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="D683" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A684" s="1">
+        <v>45876</v>
+      </c>
+      <c r="B684" t="s">
+        <v>272</v>
+      </c>
+      <c r="C684" s="2">
+        <v>6.27</v>
+      </c>
+      <c r="D684" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A685" s="1">
+        <v>45876</v>
+      </c>
+      <c r="B685" t="s">
+        <v>76</v>
+      </c>
+      <c r="C685" s="2">
+        <v>0.77</v>
+      </c>
+      <c r="D685" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A686" s="1">
+        <v>45876</v>
+      </c>
+      <c r="B686" t="s">
+        <v>382</v>
+      </c>
+      <c r="C686" s="2">
+        <v>0.66</v>
+      </c>
+      <c r="D686" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="687" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A687" s="1">
+        <v>45876</v>
+      </c>
+      <c r="B687" t="s">
+        <v>131</v>
+      </c>
+      <c r="C687" s="2">
+        <v>4.45</v>
+      </c>
+      <c r="D687" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A688" s="1">
+        <v>45876</v>
+      </c>
+      <c r="B688" t="s">
+        <v>106</v>
+      </c>
+      <c r="C688" s="2">
+        <v>2.98</v>
+      </c>
+      <c r="D688" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A689" s="1">
+        <v>45879</v>
+      </c>
+      <c r="B689" t="s">
+        <v>383</v>
+      </c>
+      <c r="C689" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D689" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A690" s="1">
+        <v>45879</v>
+      </c>
+      <c r="B690" t="s">
+        <v>384</v>
+      </c>
+      <c r="C690" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="D690" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A691" s="1">
+        <v>45879</v>
+      </c>
+      <c r="B691" t="s">
+        <v>106</v>
+      </c>
+      <c r="C691" s="2">
+        <v>2.95</v>
+      </c>
+      <c r="D691" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A692" s="1">
+        <v>45879</v>
+      </c>
+      <c r="B692" t="s">
+        <v>312</v>
+      </c>
+      <c r="C692" s="2">
+        <v>3.52</v>
+      </c>
+      <c r="D692" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A693" s="1">
+        <v>45879</v>
+      </c>
+      <c r="B693" t="s">
+        <v>385</v>
+      </c>
+      <c r="C693" s="2">
+        <v>0.77</v>
+      </c>
+      <c r="D693" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A694" s="1">
+        <v>45879</v>
+      </c>
+      <c r="B694" t="s">
+        <v>386</v>
+      </c>
+      <c r="C694" s="2">
+        <v>3</v>
+      </c>
+      <c r="D694" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A695" s="1">
+        <v>45879</v>
+      </c>
+      <c r="B695" t="s">
+        <v>328</v>
+      </c>
+      <c r="C695" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="D695" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A696" s="1">
+        <v>45879</v>
+      </c>
+      <c r="B696" t="s">
+        <v>112</v>
+      </c>
+      <c r="C696" s="2">
+        <v>8.35</v>
+      </c>
+      <c r="D696" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A697" s="1">
+        <v>45879</v>
+      </c>
+      <c r="B697" t="s">
+        <v>387</v>
+      </c>
+      <c r="C697" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="D697" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="698" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A698" s="1">
+        <v>45879</v>
+      </c>
+      <c r="B698" t="s">
+        <v>357</v>
+      </c>
+      <c r="C698" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="D698" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="699" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A699" s="1">
+        <v>45879</v>
+      </c>
+      <c r="B699" t="s">
+        <v>212</v>
+      </c>
+      <c r="C699" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="D699" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="700" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A700" s="1">
+        <v>45886</v>
+      </c>
+      <c r="B700" t="s">
+        <v>388</v>
+      </c>
+      <c r="C700" s="2">
+        <v>10.9</v>
+      </c>
+      <c r="D700" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="701" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A701" s="1">
+        <v>45886</v>
+      </c>
+      <c r="B701" t="s">
+        <v>389</v>
+      </c>
+      <c r="C701" s="2">
+        <v>20.9</v>
+      </c>
+      <c r="D701" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="702" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A702" s="1">
+        <v>45886</v>
+      </c>
+      <c r="B702" t="s">
+        <v>367</v>
+      </c>
+      <c r="C702" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="D702" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="703" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A703" s="1">
+        <v>45886</v>
+      </c>
+      <c r="B703" t="s">
+        <v>108</v>
+      </c>
+      <c r="C703" s="2">
+        <v>0.62</v>
+      </c>
+      <c r="D703" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="704" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A704" s="1">
+        <v>45886</v>
+      </c>
+      <c r="B704" t="s">
+        <v>140</v>
+      </c>
+      <c r="C704" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="D704" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="705" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A705" s="1">
+        <v>45886</v>
+      </c>
+      <c r="B705" t="s">
+        <v>306</v>
+      </c>
+      <c r="C705" s="2">
+        <v>5.45</v>
+      </c>
+      <c r="D705" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="706" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A706" s="1">
+        <v>45891</v>
+      </c>
+      <c r="B706" t="s">
+        <v>390</v>
+      </c>
+      <c r="C706" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="D706" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="707" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A707" s="1">
+        <v>45891</v>
+      </c>
+      <c r="B707" t="s">
+        <v>391</v>
+      </c>
+      <c r="C707" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="D707" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="708" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A708" s="1">
+        <v>45891</v>
+      </c>
+      <c r="B708" t="s">
+        <v>392</v>
+      </c>
+      <c r="C708" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="D708" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="709" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A709" s="1">
+        <v>45891</v>
+      </c>
+      <c r="B709" t="s">
+        <v>330</v>
+      </c>
+      <c r="C709" s="2">
+        <v>1.07</v>
+      </c>
+      <c r="D709" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="710" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A710" s="1">
+        <v>45891</v>
+      </c>
+      <c r="B710" t="s">
+        <v>342</v>
+      </c>
+      <c r="C710" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="D710" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="711" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A711" s="1">
+        <v>45891</v>
+      </c>
+      <c r="B711" t="s">
+        <v>272</v>
+      </c>
+      <c r="C711" s="2">
+        <v>6.58</v>
+      </c>
+      <c r="D711" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="712" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A712" s="1">
+        <v>45891</v>
+      </c>
+      <c r="B712" t="s">
+        <v>393</v>
+      </c>
+      <c r="C712" s="2">
+        <v>14.9</v>
+      </c>
+      <c r="D712" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="713" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A713" s="1">
+        <v>45891</v>
+      </c>
+      <c r="B713" t="s">
+        <v>377</v>
+      </c>
+      <c r="C713" s="2">
+        <v>13.95</v>
+      </c>
+      <c r="D713" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="714" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A714" s="1">
+        <v>45891</v>
+      </c>
+      <c r="B714" t="s">
+        <v>394</v>
+      </c>
+      <c r="C714" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="D714" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="715" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A715" s="1">
+        <v>45899</v>
+      </c>
+      <c r="B715" t="s">
+        <v>323</v>
+      </c>
+      <c r="C715" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="D715" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="716" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A716" s="1">
+        <v>45899</v>
+      </c>
+      <c r="B716" t="s">
+        <v>367</v>
+      </c>
+      <c r="C716" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="D716" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="717" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A717" s="1">
+        <v>45899</v>
+      </c>
+      <c r="B717" t="s">
+        <v>367</v>
+      </c>
+      <c r="C717" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="D717" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="718" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A718" s="1">
+        <v>45899</v>
+      </c>
+      <c r="B718" t="s">
+        <v>310</v>
+      </c>
+      <c r="C718" s="2">
+        <v>6.86</v>
+      </c>
+      <c r="D718" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="719" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A719" s="1">
+        <v>45899</v>
+      </c>
+      <c r="B719" t="s">
+        <v>357</v>
+      </c>
+      <c r="C719" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="D719" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="720" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A720" s="1">
+        <v>45899</v>
+      </c>
+      <c r="B720" t="s">
+        <v>396</v>
+      </c>
+      <c r="C720" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="D720" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="721" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A721" s="1">
+        <v>45899</v>
+      </c>
+      <c r="B721" t="s">
+        <v>306</v>
+      </c>
+      <c r="C721" s="2">
+        <v>5.45</v>
+      </c>
+      <c r="D721" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="722" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A722" s="1">
+        <v>45899</v>
+      </c>
+      <c r="B722" t="s">
+        <v>244</v>
+      </c>
+      <c r="C722" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="D722" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="723" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A723" s="1">
+        <v>45899</v>
+      </c>
+      <c r="B723" t="s">
+        <v>212</v>
+      </c>
+      <c r="C723" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="D723" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="724" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A724" s="1">
+        <v>45910</v>
+      </c>
+      <c r="B724" t="s">
+        <v>310</v>
+      </c>
+      <c r="C724" s="2">
+        <v>7.72</v>
+      </c>
+      <c r="D724" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="725" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A725" s="1">
+        <v>45910</v>
+      </c>
+      <c r="B725" t="s">
+        <v>106</v>
+      </c>
+      <c r="C725" s="2">
+        <v>2.84</v>
+      </c>
+      <c r="D725" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="726" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A726" s="1">
+        <v>45910</v>
+      </c>
+      <c r="B726" t="s">
+        <v>131</v>
+      </c>
+      <c r="C726" s="2">
+        <v>4.68</v>
+      </c>
+      <c r="D726" t="s">
         <v>22</v>
       </c>
     </row>
@@ -10888,7 +11926,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47AC92D9-8D81-4D6D-9D00-CF5410D2E104}">
-  <dimension ref="A2:I100"/>
+  <dimension ref="A2:I109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" customWidth="1"/>
@@ -11719,23 +12757,94 @@
     <row r="96" spans="2:7" x14ac:dyDescent="0.25">
       <c r="G96" s="23"/>
     </row>
-    <row r="97" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:7" x14ac:dyDescent="0.25">
       <c r="G97" s="23" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="98" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:7" x14ac:dyDescent="0.25">
       <c r="G98" s="23" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="99" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
       <c r="G99" s="23" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="100" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:7" x14ac:dyDescent="0.25">
       <c r="G100" s="23"/>
+    </row>
+    <row r="101" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B101" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B102" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C102" s="10">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B103" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C103" s="8">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B104" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C104" s="10">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B105" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C105" s="8">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B106" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C106" s="10">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B107" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C107" s="8">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B108" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C108" s="10">
+        <v>13.95</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C109" s="11">
+        <f>SUM(C103:C108)</f>
+        <v>46.019999999999996</v>
+      </c>
+      <c r="D109">
+        <f>46.02/5</f>
+        <v>9.2040000000000006</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Groceries.xlsx
+++ b/Groceries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a960143ed076ae3/Desktop/Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3066" documentId="8_{98EF138E-B783-427A-B5F9-8CBFC75A152E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55273673-A45B-45C0-816D-550EEEA274E9}"/>
+  <xr:revisionPtr revIDLastSave="3341" documentId="8_{98EF138E-B783-427A-B5F9-8CBFC75A152E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE958E8B-4223-4FFC-AD29-B893374829E8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4658677F-DFAC-47A2-8C6E-7C4307640A24}"/>
+    <workbookView xWindow="-28920" yWindow="1830" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{4658677F-DFAC-47A2-8C6E-7C4307640A24}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1673" uniqueCount="424">
   <si>
     <t>Date</t>
   </si>
@@ -1242,6 +1242,87 @@
   </si>
   <si>
     <t>ZUS SIGN MIXES COFFEE - DOLCE LATTE</t>
+  </si>
+  <si>
+    <t>PREMIER KITCHEN TOWEL 60SX6ROLLS *1</t>
+  </si>
+  <si>
+    <t>YARRA F FRESH FULL CREAM MILK UHT 1L</t>
+  </si>
+  <si>
+    <t>SHOKUBUTSU CLEAN FRESH ORANGE ZEST 800G REF</t>
+  </si>
+  <si>
+    <t>COLES JAM STRAWBERRY 450G</t>
+  </si>
+  <si>
+    <t>TM TOFO GORENG 3PS (MYS) P10</t>
+  </si>
+  <si>
+    <t>SAN REMO CREAMY MUSHROOM &amp; UNION 120G *1</t>
+  </si>
+  <si>
+    <t>IKAN TALAPIA MERAH L</t>
+  </si>
+  <si>
+    <t>CUCUMBER (TIMUN) (MYS)</t>
+  </si>
+  <si>
+    <t>MF PARSLET FLAKES 4G *1</t>
+  </si>
+  <si>
+    <t>MCCORMICK CHILI FLAKES 29G</t>
+  </si>
+  <si>
+    <t>KAPAL AIR GULA MELAKA 18SX22G</t>
+  </si>
+  <si>
+    <t>GOODAY FULL CREAM UNIT MILK 1LIT *1</t>
+  </si>
+  <si>
+    <t>FARMCOWS DAIRY SPREAD 250G *1</t>
+  </si>
+  <si>
+    <t>SERI MURNI 1KG *1</t>
+  </si>
+  <si>
+    <t>IKAN KEMBONG BATU M</t>
+  </si>
+  <si>
+    <t>AYAM MACKAREL IN TOMATO(B) 230GM *1</t>
+  </si>
+  <si>
+    <t>GINGEROLD HALIA TUA (THA) KG</t>
+  </si>
+  <si>
+    <t>GOODAY FUULL CREAM UHT MILK 1LIT *1</t>
+  </si>
+  <si>
+    <t>DARA PRIMA 70 CHICKEN BURRGERR 6X70G</t>
+  </si>
+  <si>
+    <t>EMBORG PERFECT BURGER SLICES 200G</t>
+  </si>
+  <si>
+    <t>PERFECT ITALIANO PERFECT PIZZA 150G</t>
+  </si>
+  <si>
+    <t>HAPPYEGG OMEGA PLUS LUTEIN 10S</t>
+  </si>
+  <si>
+    <t>FRENCH LOAF *1</t>
+  </si>
+  <si>
+    <t>BITAGEN ASSORTED (1X5SX125ML) *1</t>
+  </si>
+  <si>
+    <t>KICKAPOO JOY JUICE 1.5LIT *1</t>
+  </si>
+  <si>
+    <t>ROKEBY PROTEIN DUTCH CHOCOLATE 425ML</t>
+  </si>
+  <si>
+    <t>GARLIC BREAD</t>
   </si>
 </sst>
 </file>
@@ -1432,8 +1513,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CF63E7CD-18A2-4918-AE48-6D9DD5DB55B7}" name="Table1" displayName="Table1" ref="A1:D726" totalsRowShown="0">
-  <autoFilter ref="A1:D726" xr:uid="{CF63E7CD-18A2-4918-AE48-6D9DD5DB55B7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CF63E7CD-18A2-4918-AE48-6D9DD5DB55B7}" name="Table1" displayName="Table1" ref="A1:D781" totalsRowShown="0">
+  <autoFilter ref="A1:D781" xr:uid="{CF63E7CD-18A2-4918-AE48-6D9DD5DB55B7}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{3FF5C65C-C3A8-4E20-8338-7D6593C60B8B}" name="Date" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{E2DBD41B-ADF3-48D8-839D-9E340056EB1F}" name="Grocery Item"/>
@@ -1741,7 +1822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F1FE89E-F524-4366-B417-1C841F4683A9}">
-  <dimension ref="A1:D726"/>
+  <dimension ref="A1:D781"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -11911,6 +11992,776 @@
         <v>4.68</v>
       </c>
       <c r="D726" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="727" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A727" s="1">
+        <v>45916</v>
+      </c>
+      <c r="B727" t="s">
+        <v>397</v>
+      </c>
+      <c r="C727" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="D727" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="728" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A728" s="1">
+        <v>45916</v>
+      </c>
+      <c r="B728" t="s">
+        <v>49</v>
+      </c>
+      <c r="C728" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="D728" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="729" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A729" s="1">
+        <v>45916</v>
+      </c>
+      <c r="B729" t="s">
+        <v>398</v>
+      </c>
+      <c r="C729" s="2">
+        <v>5.49</v>
+      </c>
+      <c r="D729" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="730" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A730" s="1">
+        <v>45916</v>
+      </c>
+      <c r="B730" t="s">
+        <v>399</v>
+      </c>
+      <c r="C730" s="2">
+        <v>13.7</v>
+      </c>
+      <c r="D730" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="731" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A731" s="1">
+        <v>45916</v>
+      </c>
+      <c r="B731" t="s">
+        <v>272</v>
+      </c>
+      <c r="C731" s="2">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="D731" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="732" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A732" s="1">
+        <v>45916</v>
+      </c>
+      <c r="B732" t="s">
+        <v>400</v>
+      </c>
+      <c r="C732" s="2">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="D732" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="733" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A733" s="1">
+        <v>45916</v>
+      </c>
+      <c r="B733" t="s">
+        <v>363</v>
+      </c>
+      <c r="C733" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="D733" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="734" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A734" s="1">
+        <v>45916</v>
+      </c>
+      <c r="B734" t="s">
+        <v>328</v>
+      </c>
+      <c r="C734" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="D734" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="735" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A735" s="1">
+        <v>45916</v>
+      </c>
+      <c r="B735" t="s">
+        <v>306</v>
+      </c>
+      <c r="C735" s="2">
+        <v>5.45</v>
+      </c>
+      <c r="D735" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="736" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A736" s="1">
+        <v>45916</v>
+      </c>
+      <c r="B736" t="s">
+        <v>106</v>
+      </c>
+      <c r="C736" s="2">
+        <v>2.48</v>
+      </c>
+      <c r="D736" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="737" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A737" s="1">
+        <v>45916</v>
+      </c>
+      <c r="B737" t="s">
+        <v>401</v>
+      </c>
+      <c r="C737" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="D737" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="738" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A738" s="1">
+        <v>45916</v>
+      </c>
+      <c r="B738" t="s">
+        <v>396</v>
+      </c>
+      <c r="C738" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="D738" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="739" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A739" s="1">
+        <v>45916</v>
+      </c>
+      <c r="B739" t="s">
+        <v>108</v>
+      </c>
+      <c r="C739" s="2">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="D739" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="740" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A740" s="1">
+        <v>45927</v>
+      </c>
+      <c r="B740" t="s">
+        <v>396</v>
+      </c>
+      <c r="C740" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="D740" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="741" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A741" s="1">
+        <v>45927</v>
+      </c>
+      <c r="B741" t="s">
+        <v>357</v>
+      </c>
+      <c r="C741" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="D741" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="742" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A742" s="1">
+        <v>45927</v>
+      </c>
+      <c r="B742" t="s">
+        <v>310</v>
+      </c>
+      <c r="C742" s="2">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="D742" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="743" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A743" s="1">
+        <v>45927</v>
+      </c>
+      <c r="B743" t="s">
+        <v>391</v>
+      </c>
+      <c r="C743" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="D743" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="744" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A744" s="1">
+        <v>45927</v>
+      </c>
+      <c r="B744" t="s">
+        <v>374</v>
+      </c>
+      <c r="C744" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="D744" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="745" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A745" s="1">
+        <v>45927</v>
+      </c>
+      <c r="B745" t="s">
+        <v>212</v>
+      </c>
+      <c r="C745" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="D745" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="746" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A746" s="1">
+        <v>45927</v>
+      </c>
+      <c r="B746" t="s">
+        <v>402</v>
+      </c>
+      <c r="C746" s="2">
+        <v>4.59</v>
+      </c>
+      <c r="D746" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="747" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A747" s="1">
+        <v>45927</v>
+      </c>
+      <c r="B747" t="s">
+        <v>330</v>
+      </c>
+      <c r="C747" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="D747" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="748" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A748" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B748" t="s">
+        <v>403</v>
+      </c>
+      <c r="C748" s="2">
+        <v>13.33</v>
+      </c>
+      <c r="D748" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="749" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A749" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B749" t="s">
+        <v>404</v>
+      </c>
+      <c r="C749" s="2">
+        <v>1.67</v>
+      </c>
+      <c r="D749" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="750" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A750" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B750" t="s">
+        <v>140</v>
+      </c>
+      <c r="C750" s="2">
+        <v>0.34</v>
+      </c>
+      <c r="D750" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="751" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A751" s="1">
+        <v>45935</v>
+      </c>
+      <c r="B751" t="s">
+        <v>405</v>
+      </c>
+      <c r="C751" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="D751" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="752" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A752" s="1">
+        <v>45935</v>
+      </c>
+      <c r="B752" t="s">
+        <v>406</v>
+      </c>
+      <c r="C752" s="2">
+        <v>13.9</v>
+      </c>
+      <c r="D752" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="753" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A753" s="1">
+        <v>45937</v>
+      </c>
+      <c r="B753" t="s">
+        <v>357</v>
+      </c>
+      <c r="C753" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="D753" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="754" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A754" s="1">
+        <v>45937</v>
+      </c>
+      <c r="B754" t="s">
+        <v>407</v>
+      </c>
+      <c r="C754" s="2">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="D754" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="755" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A755" s="1">
+        <v>45937</v>
+      </c>
+      <c r="B755" t="s">
+        <v>408</v>
+      </c>
+      <c r="C755" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="D755" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="756" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A756" s="1">
+        <v>45937</v>
+      </c>
+      <c r="B756" t="s">
+        <v>212</v>
+      </c>
+      <c r="C756" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="D756" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="757" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A757" s="1">
+        <v>45942</v>
+      </c>
+      <c r="B757" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C757" s="2">
+        <v>5.95</v>
+      </c>
+      <c r="D757" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="758" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A758" s="1">
+        <v>45942</v>
+      </c>
+      <c r="B758" t="s">
+        <v>410</v>
+      </c>
+      <c r="C758" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="D758" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="759" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A759" s="1">
+        <v>45942</v>
+      </c>
+      <c r="B759" t="s">
+        <v>49</v>
+      </c>
+      <c r="C759" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="D759" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="760" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A760" s="1">
+        <v>45942</v>
+      </c>
+      <c r="B760" t="s">
+        <v>342</v>
+      </c>
+      <c r="C760" s="2">
+        <v>1.02</v>
+      </c>
+      <c r="D760" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="761" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A761" s="1">
+        <v>45942</v>
+      </c>
+      <c r="B761" t="s">
+        <v>411</v>
+      </c>
+      <c r="C761" s="2">
+        <v>3.63</v>
+      </c>
+      <c r="D761" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="762" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A762" s="1">
+        <v>45942</v>
+      </c>
+      <c r="B762" t="s">
+        <v>404</v>
+      </c>
+      <c r="C762" s="2">
+        <v>0.91</v>
+      </c>
+      <c r="D762" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="763" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A763" s="1">
+        <v>45942</v>
+      </c>
+      <c r="B763" t="s">
+        <v>412</v>
+      </c>
+      <c r="C763" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="D763" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="764" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A764" s="1">
+        <v>45942</v>
+      </c>
+      <c r="B764" t="s">
+        <v>212</v>
+      </c>
+      <c r="C764" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="D764" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="765" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A765" s="1">
+        <v>45946</v>
+      </c>
+      <c r="B765" t="s">
+        <v>112</v>
+      </c>
+      <c r="C765" s="2">
+        <v>7.95</v>
+      </c>
+      <c r="D765" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="766" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A766" s="1">
+        <v>45946</v>
+      </c>
+      <c r="B766" t="s">
+        <v>106</v>
+      </c>
+      <c r="C766" s="2">
+        <v>3.03</v>
+      </c>
+      <c r="D766" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="767" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A767" s="1">
+        <v>45946</v>
+      </c>
+      <c r="B767" t="s">
+        <v>413</v>
+      </c>
+      <c r="C767" s="2">
+        <v>0.64</v>
+      </c>
+      <c r="D767" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="768" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A768" s="1">
+        <v>45946</v>
+      </c>
+      <c r="B768" t="s">
+        <v>342</v>
+      </c>
+      <c r="C768" s="2">
+        <v>0.92</v>
+      </c>
+      <c r="D768" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="769" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A769" s="1">
+        <v>45946</v>
+      </c>
+      <c r="B769" t="s">
+        <v>131</v>
+      </c>
+      <c r="C769" s="2">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="D769" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="770" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A770" s="1">
+        <v>45955</v>
+      </c>
+      <c r="B770" t="s">
+        <v>414</v>
+      </c>
+      <c r="C770" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="D770" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="771" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A771" s="1">
+        <v>45955</v>
+      </c>
+      <c r="B771" t="s">
+        <v>415</v>
+      </c>
+      <c r="C771" s="2">
+        <v>10</v>
+      </c>
+      <c r="D771" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="772" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A772" s="1">
+        <v>45955</v>
+      </c>
+      <c r="B772" t="s">
+        <v>416</v>
+      </c>
+      <c r="C772" s="2">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="D772" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="773" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A773" s="1">
+        <v>45955</v>
+      </c>
+      <c r="B773" t="s">
+        <v>417</v>
+      </c>
+      <c r="C773" s="2">
+        <v>13</v>
+      </c>
+      <c r="D773" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="774" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A774" s="1">
+        <v>45955</v>
+      </c>
+      <c r="B774" t="s">
+        <v>418</v>
+      </c>
+      <c r="C774" s="2">
+        <v>7.45</v>
+      </c>
+      <c r="D774" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="775" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A775" s="1">
+        <v>45955</v>
+      </c>
+      <c r="B775" t="s">
+        <v>419</v>
+      </c>
+      <c r="C775" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D775" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="776" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A776" s="1">
+        <v>45955</v>
+      </c>
+      <c r="B776" t="s">
+        <v>244</v>
+      </c>
+      <c r="C776" s="2">
+        <v>1.19</v>
+      </c>
+      <c r="D776" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="777" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A777" s="1">
+        <v>45955</v>
+      </c>
+      <c r="B777" t="s">
+        <v>330</v>
+      </c>
+      <c r="C777" s="2">
+        <v>0.93</v>
+      </c>
+      <c r="D777" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="778" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A778" s="1">
+        <v>45955</v>
+      </c>
+      <c r="B778" t="s">
+        <v>420</v>
+      </c>
+      <c r="C778" s="2">
+        <v>5.45</v>
+      </c>
+      <c r="D778" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="779" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A779" s="1">
+        <v>45955</v>
+      </c>
+      <c r="B779" t="s">
+        <v>212</v>
+      </c>
+      <c r="C779" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="D779" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="780" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A780" s="1">
+        <v>45955</v>
+      </c>
+      <c r="B780" t="s">
+        <v>421</v>
+      </c>
+      <c r="C780" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="D780" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="781" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A781" s="1">
+        <v>45955</v>
+      </c>
+      <c r="B781" t="s">
+        <v>422</v>
+      </c>
+      <c r="C781" s="2">
+        <v>13.9</v>
+      </c>
+      <c r="D781" t="s">
         <v>22</v>
       </c>
     </row>
@@ -11926,7 +12777,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47AC92D9-8D81-4D6D-9D00-CF5410D2E104}">
-  <dimension ref="A2:I109"/>
+  <dimension ref="A2:I118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" customWidth="1"/>
@@ -12846,6 +13697,65 @@
         <v>9.2040000000000006</v>
       </c>
     </row>
+    <row r="113" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B113" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B114" t="s">
+        <v>342</v>
+      </c>
+      <c r="C114">
+        <v>0.92</v>
+      </c>
+      <c r="D114">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B115" t="s">
+        <v>419</v>
+      </c>
+      <c r="C115">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D115">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B116" t="s">
+        <v>409</v>
+      </c>
+      <c r="C116">
+        <v>5.95</v>
+      </c>
+      <c r="D116">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B117" t="s">
+        <v>405</v>
+      </c>
+      <c r="C117">
+        <v>9.1</v>
+      </c>
+      <c r="D117">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C118">
+        <f>SUM(C114:C117)</f>
+        <v>20.869999999999997</v>
+      </c>
+      <c r="D118">
+        <f>SUM(D114:D117)</f>
+        <v>9.02</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="G74:G87"/>

--- a/Groceries.xlsx
+++ b/Groceries.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a960143ed076ae3/Desktop/Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3341" documentId="8_{98EF138E-B783-427A-B5F9-8CBFC75A152E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE958E8B-4223-4FFC-AD29-B893374829E8}"/>
+  <xr:revisionPtr revIDLastSave="3702" documentId="8_{98EF138E-B783-427A-B5F9-8CBFC75A152E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0FBD3FE-CBF6-463A-BD95-86507691771B}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1830" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{4658677F-DFAC-47A2-8C6E-7C4307640A24}"/>
+    <workbookView xWindow="-28920" yWindow="1830" windowWidth="29040" windowHeight="15840" xr2:uid="{4658677F-DFAC-47A2-8C6E-7C4307640A24}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Recipe" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1673" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="481">
   <si>
     <t>Date</t>
   </si>
@@ -1323,6 +1324,177 @@
   </si>
   <si>
     <t>GARLIC BREAD</t>
+  </si>
+  <si>
+    <t>QL BRAIN+ EGG (M) 15 *S</t>
+  </si>
+  <si>
+    <t>SAN REMO QUICK COOK MACARONI 500G</t>
+  </si>
+  <si>
+    <t>sewa</t>
+  </si>
+  <si>
+    <t>electric</t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>celcom</t>
+  </si>
+  <si>
+    <t>asb</t>
+  </si>
+  <si>
+    <t>insurance</t>
+  </si>
+  <si>
+    <t>seyi</t>
+  </si>
+  <si>
+    <t>sabah election</t>
+  </si>
+  <si>
+    <t>motor lesen</t>
+  </si>
+  <si>
+    <t>extra paid for motor lesen</t>
+  </si>
+  <si>
+    <t>shopee</t>
+  </si>
+  <si>
+    <t>grab</t>
+  </si>
+  <si>
+    <t>daily expense</t>
+  </si>
+  <si>
+    <t>rafizi</t>
+  </si>
+  <si>
+    <t>wifi</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>gaji</t>
+  </si>
+  <si>
+    <t>baki</t>
+  </si>
+  <si>
+    <t>ORCHID FRUITALE SOAP (CALAMA) 3/S 70G</t>
+  </si>
+  <si>
+    <t>KOPIKO CREAMY LATTE 20 X 24G</t>
+  </si>
+  <si>
+    <t>CHICKEN WHOLE LEG ABF</t>
+  </si>
+  <si>
+    <t>MARIGOLD FULL CREAM MILK 1LIT *1</t>
+  </si>
+  <si>
+    <t>MASSIMO SANDWICH LOAF (WHEAT GERM) 400G *1</t>
+  </si>
+  <si>
+    <t>DL UHT FRESH MILK 1LIT *1</t>
+  </si>
+  <si>
+    <t>SUNSHINE SHIRO CHOCO HOKKAIDO MILK CREAM R 0LL 52G</t>
+  </si>
+  <si>
+    <t>LOTUS SWI</t>
+  </si>
+  <si>
+    <t>FRZ CHICKE</t>
+  </si>
+  <si>
+    <t>LOTUSS TOM</t>
+  </si>
+  <si>
+    <t>BAWANG KUN</t>
+  </si>
+  <si>
+    <t>TIRAMISU M</t>
+  </si>
+  <si>
+    <t>KINDER BUE</t>
+  </si>
+  <si>
+    <t>DL UHT LOW FAT MILK 1LIT *1</t>
+  </si>
+  <si>
+    <t>GOODDAY FULL CREAM UHT MILK 1LIT *1</t>
+  </si>
+  <si>
+    <t>FARM FRESH GREEK ORIGINAL 120G</t>
+  </si>
+  <si>
+    <t>WE.LOAF.BREAD SUNFLOWER PREMIUM WHOLEMEAL 515G</t>
+  </si>
+  <si>
+    <t>SIA BEBOLA IKAN PARANG 16S *1</t>
+  </si>
+  <si>
+    <t>YK SIEW PAK CHOY 250G (MYS) P10</t>
+  </si>
+  <si>
+    <t>PF TOMATO-HOLLAND 400G (MYS) P12</t>
+  </si>
+  <si>
+    <t>D'FRESH EGGS LARGE (10S) *1</t>
+  </si>
+  <si>
+    <t>DL UHT CREAM MILK 1LIT *1</t>
+  </si>
+  <si>
+    <t>GINGER OLD HALIA TUA (THA) K9</t>
+  </si>
+  <si>
+    <t>FERRY POMPRET FISH SAUCE 200CC *1</t>
+  </si>
+  <si>
+    <t>BAYGON CC AEROSOL 270ML *1</t>
+  </si>
+  <si>
+    <t>CG SPRING ONION (DAUN BAWANG) 80G (MYS)</t>
+  </si>
+  <si>
+    <t>GARDENIA SOMMERSET COTTAGE 300G *1</t>
+  </si>
+  <si>
+    <t>DL UHT FULL CREAM MILK 1LIT *1</t>
+  </si>
+  <si>
+    <t>PF CHERRY TOMATO-PLUM 350 (MYS) P12</t>
+  </si>
+  <si>
+    <t>LIFE TOMATO SAUCE 350ML *1</t>
+  </si>
+  <si>
+    <t>CED SQUEEZE PURE HONEY 500G *1</t>
+  </si>
+  <si>
+    <t>BAWANG BESAR MERAH *1</t>
+  </si>
+  <si>
+    <t>LEMON C88</t>
+  </si>
+  <si>
+    <t>MCCORMICK OREGANO 10G</t>
+  </si>
+  <si>
+    <t>CHICKEN SAUSAGE  CHEESE BUN *1</t>
+  </si>
+  <si>
+    <t>LEMON BAKED CHICKEN</t>
+  </si>
+  <si>
+    <t>ayam</t>
   </si>
 </sst>
 </file>
@@ -1344,7 +1516,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1360,6 +1532,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1437,7 +1615,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1480,6 +1658,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1513,8 +1695,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CF63E7CD-18A2-4918-AE48-6D9DD5DB55B7}" name="Table1" displayName="Table1" ref="A1:D781" totalsRowShown="0">
-  <autoFilter ref="A1:D781" xr:uid="{CF63E7CD-18A2-4918-AE48-6D9DD5DB55B7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CF63E7CD-18A2-4918-AE48-6D9DD5DB55B7}" name="Table1" displayName="Table1" ref="A1:D843" totalsRowShown="0">
+  <autoFilter ref="A1:D843" xr:uid="{CF63E7CD-18A2-4918-AE48-6D9DD5DB55B7}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{3FF5C65C-C3A8-4E20-8338-7D6593C60B8B}" name="Date" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{E2DBD41B-ADF3-48D8-839D-9E340056EB1F}" name="Grocery Item"/>
@@ -1822,7 +2004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F1FE89E-F524-4366-B417-1C841F4683A9}">
-  <dimension ref="A1:D781"/>
+  <dimension ref="A1:D843"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -12762,6 +12944,874 @@
         <v>13.9</v>
       </c>
       <c r="D781" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="782" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A782" s="1">
+        <v>45963</v>
+      </c>
+      <c r="B782" t="s">
+        <v>424</v>
+      </c>
+      <c r="C782" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="D782" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="783" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A783" s="1">
+        <v>45963</v>
+      </c>
+      <c r="B783" t="s">
+        <v>425</v>
+      </c>
+      <c r="C783" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="D783" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="784" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A784" s="1">
+        <v>45963</v>
+      </c>
+      <c r="B784" t="s">
+        <v>272</v>
+      </c>
+      <c r="C784" s="2">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="D784" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="785" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A785" s="1">
+        <v>45963</v>
+      </c>
+      <c r="B785" t="s">
+        <v>330</v>
+      </c>
+      <c r="C785" s="2">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="D785" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="786" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A786" s="1">
+        <v>45963</v>
+      </c>
+      <c r="B786" t="s">
+        <v>244</v>
+      </c>
+      <c r="C786" s="2">
+        <v>3.82</v>
+      </c>
+      <c r="D786" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="787" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A787" s="1">
+        <v>45963</v>
+      </c>
+      <c r="B787" t="s">
+        <v>212</v>
+      </c>
+      <c r="C787" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="D787" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="788" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A788" s="1">
+        <v>45971</v>
+      </c>
+      <c r="B788" t="s">
+        <v>444</v>
+      </c>
+      <c r="C788" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="D788" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="789" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A789" s="1">
+        <v>45971</v>
+      </c>
+      <c r="B789" t="s">
+        <v>445</v>
+      </c>
+      <c r="C789" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="D789" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="790" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A790" s="1">
+        <v>45971</v>
+      </c>
+      <c r="B790" t="s">
+        <v>446</v>
+      </c>
+      <c r="C790" s="2">
+        <v>11.66</v>
+      </c>
+      <c r="D790" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="791" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A791" s="1">
+        <v>45971</v>
+      </c>
+      <c r="B791" t="s">
+        <v>447</v>
+      </c>
+      <c r="C791" s="2">
+        <v>7.3</v>
+      </c>
+      <c r="D791" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="792" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A792" s="1">
+        <v>45971</v>
+      </c>
+      <c r="B792" t="s">
+        <v>448</v>
+      </c>
+      <c r="C792" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="D792" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="793" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A793" s="1">
+        <v>45971</v>
+      </c>
+      <c r="B793" t="s">
+        <v>449</v>
+      </c>
+      <c r="C793" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="D793" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="794" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A794" s="1">
+        <v>45971</v>
+      </c>
+      <c r="B794" t="s">
+        <v>450</v>
+      </c>
+      <c r="C794" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="D794" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="795" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A795" s="1">
+        <v>45971</v>
+      </c>
+      <c r="B795" t="s">
+        <v>131</v>
+      </c>
+      <c r="C795" s="2">
+        <v>3.36</v>
+      </c>
+      <c r="D795" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="796" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A796" s="1">
+        <v>45971</v>
+      </c>
+      <c r="B796" t="s">
+        <v>106</v>
+      </c>
+      <c r="C796" s="2">
+        <v>2.83</v>
+      </c>
+      <c r="D796" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="797" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A797" s="1">
+        <v>45972</v>
+      </c>
+      <c r="B797" t="s">
+        <v>240</v>
+      </c>
+      <c r="C797" s="2">
+        <v>7.49</v>
+      </c>
+      <c r="D797" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="798" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A798" s="1">
+        <v>45983</v>
+      </c>
+      <c r="B798" t="s">
+        <v>451</v>
+      </c>
+      <c r="C798" s="2">
+        <v>16.989999999999998</v>
+      </c>
+      <c r="D798" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="799" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A799" s="1">
+        <v>45983</v>
+      </c>
+      <c r="B799" t="s">
+        <v>452</v>
+      </c>
+      <c r="C799" s="2">
+        <v>21.85</v>
+      </c>
+      <c r="D799" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="800" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A800" s="1">
+        <v>45983</v>
+      </c>
+      <c r="B800" t="s">
+        <v>453</v>
+      </c>
+      <c r="C800" s="2">
+        <v>2.99</v>
+      </c>
+      <c r="D800" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="801" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A801" s="1">
+        <v>45983</v>
+      </c>
+      <c r="B801" t="s">
+        <v>453</v>
+      </c>
+      <c r="C801" s="2">
+        <v>2.99</v>
+      </c>
+      <c r="D801" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="802" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A802" s="1">
+        <v>45983</v>
+      </c>
+      <c r="B802" t="s">
+        <v>454</v>
+      </c>
+      <c r="C802" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="D802" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="803" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A803" s="1">
+        <v>45983</v>
+      </c>
+      <c r="B803" t="s">
+        <v>455</v>
+      </c>
+      <c r="C803" s="2">
+        <v>8</v>
+      </c>
+      <c r="D803" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="804" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A804" s="1">
+        <v>45983</v>
+      </c>
+      <c r="B804" t="s">
+        <v>456</v>
+      </c>
+      <c r="C804" s="2">
+        <v>9.85</v>
+      </c>
+      <c r="D804" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="805" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A805" s="1">
+        <v>45990</v>
+      </c>
+      <c r="B805" t="s">
+        <v>357</v>
+      </c>
+      <c r="C805" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="D805" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="806" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A806" s="1">
+        <v>45990</v>
+      </c>
+      <c r="B806" t="s">
+        <v>457</v>
+      </c>
+      <c r="C806" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="D806" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="807" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A807" s="1">
+        <v>45990</v>
+      </c>
+      <c r="B807" t="s">
+        <v>458</v>
+      </c>
+      <c r="C807" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="D807" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="808" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A808" s="1">
+        <v>45990</v>
+      </c>
+      <c r="B808" t="s">
+        <v>459</v>
+      </c>
+      <c r="C808" s="2">
+        <v>4</v>
+      </c>
+      <c r="D808" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="809" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A809" s="1">
+        <v>45990</v>
+      </c>
+      <c r="B809" t="s">
+        <v>460</v>
+      </c>
+      <c r="C809" s="2">
+        <v>11.8</v>
+      </c>
+      <c r="D809" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="810" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A810" s="1">
+        <v>45996</v>
+      </c>
+      <c r="B810" t="s">
+        <v>461</v>
+      </c>
+      <c r="C810" s="2">
+        <v>4</v>
+      </c>
+      <c r="D810" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="811" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A811" s="1">
+        <v>45996</v>
+      </c>
+      <c r="B811" t="s">
+        <v>462</v>
+      </c>
+      <c r="C811" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="D811" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="812" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A812" s="1">
+        <v>45996</v>
+      </c>
+      <c r="B812" t="s">
+        <v>463</v>
+      </c>
+      <c r="C812" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="D812" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="813" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A813" s="1">
+        <v>45996</v>
+      </c>
+      <c r="B813" t="s">
+        <v>464</v>
+      </c>
+      <c r="C813" s="2">
+        <v>8</v>
+      </c>
+      <c r="D813" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="814" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A814" s="1">
+        <v>45996</v>
+      </c>
+      <c r="B814" t="s">
+        <v>312</v>
+      </c>
+      <c r="C814" s="2">
+        <v>3.45</v>
+      </c>
+      <c r="D814" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="815" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A815" s="1">
+        <v>45996</v>
+      </c>
+      <c r="B815" t="s">
+        <v>330</v>
+      </c>
+      <c r="C815" s="2">
+        <v>0.62</v>
+      </c>
+      <c r="D815" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="816" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A816" s="1">
+        <v>45996</v>
+      </c>
+      <c r="B816" t="s">
+        <v>342</v>
+      </c>
+      <c r="C816" s="2">
+        <v>1.02</v>
+      </c>
+      <c r="D816" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="817" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A817" s="1">
+        <v>45996</v>
+      </c>
+      <c r="B817" t="s">
+        <v>140</v>
+      </c>
+      <c r="C817" s="2">
+        <v>0.37</v>
+      </c>
+      <c r="D817" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="818" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A818" s="1">
+        <v>45996</v>
+      </c>
+      <c r="B818" t="s">
+        <v>106</v>
+      </c>
+      <c r="C818" s="2">
+        <v>2.41</v>
+      </c>
+      <c r="D818" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="819" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A819" s="1">
+        <v>46002</v>
+      </c>
+      <c r="B819" t="s">
+        <v>445</v>
+      </c>
+      <c r="C819" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="D819" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="820" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A820" s="1">
+        <v>46002</v>
+      </c>
+      <c r="B820" t="s">
+        <v>465</v>
+      </c>
+      <c r="C820" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="D820" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="821" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A821" s="1">
+        <v>46002</v>
+      </c>
+      <c r="B821" t="s">
+        <v>343</v>
+      </c>
+      <c r="C821" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="D821" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="822" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A822" s="1">
+        <v>46002</v>
+      </c>
+      <c r="B822" t="s">
+        <v>179</v>
+      </c>
+      <c r="C822" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="D822" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="823" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A823" s="1">
+        <v>46002</v>
+      </c>
+      <c r="B823" t="s">
+        <v>466</v>
+      </c>
+      <c r="C823" s="2">
+        <v>0.49</v>
+      </c>
+      <c r="D823" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="824" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A824" s="1">
+        <v>46002</v>
+      </c>
+      <c r="B824" t="s">
+        <v>467</v>
+      </c>
+      <c r="C824" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="D824" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="825" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A825" s="1">
+        <v>46002</v>
+      </c>
+      <c r="B825" t="s">
+        <v>245</v>
+      </c>
+      <c r="C825" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="D825" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="826" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A826" s="1">
+        <v>46002</v>
+      </c>
+      <c r="B826" t="s">
+        <v>468</v>
+      </c>
+      <c r="C826" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="D826" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="827" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A827" s="1">
+        <v>46002</v>
+      </c>
+      <c r="B827" t="s">
+        <v>334</v>
+      </c>
+      <c r="C827" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="D827" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="828" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A828" s="1">
+        <v>46002</v>
+      </c>
+      <c r="B828" t="s">
+        <v>469</v>
+      </c>
+      <c r="C828" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="D828" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="829" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A829" s="1">
+        <v>46002</v>
+      </c>
+      <c r="B829" t="s">
+        <v>470</v>
+      </c>
+      <c r="C829" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="D829" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="830" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A830" s="1">
+        <v>46009</v>
+      </c>
+      <c r="B830" t="s">
+        <v>212</v>
+      </c>
+      <c r="C830" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="D830" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="831" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A831" s="1">
+        <v>46009</v>
+      </c>
+      <c r="B831" t="s">
+        <v>325</v>
+      </c>
+      <c r="C831" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="D831" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="832" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A832" s="1">
+        <v>46011</v>
+      </c>
+      <c r="B832" t="s">
+        <v>457</v>
+      </c>
+      <c r="C832" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="D832" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="833" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A833" s="1">
+        <v>46011</v>
+      </c>
+      <c r="B833" t="s">
+        <v>471</v>
+      </c>
+      <c r="C833" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="D833" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="834" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A834" s="1">
+        <v>46011</v>
+      </c>
+      <c r="B834" t="s">
+        <v>472</v>
+      </c>
+      <c r="C834" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D834" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="835" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A835" s="1">
+        <v>46011</v>
+      </c>
+      <c r="B835" t="s">
+        <v>473</v>
+      </c>
+      <c r="C835" s="2">
+        <v>4.05</v>
+      </c>
+      <c r="D835" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="836" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A836" s="1">
+        <v>46011</v>
+      </c>
+      <c r="B836" t="s">
+        <v>474</v>
+      </c>
+      <c r="C836" s="2">
+        <v>14</v>
+      </c>
+      <c r="D836" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="837" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A837" s="1">
+        <v>46011</v>
+      </c>
+      <c r="B837" t="s">
+        <v>475</v>
+      </c>
+      <c r="C837" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="D837" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="838" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A838" s="1">
+        <v>46011</v>
+      </c>
+      <c r="B838" t="s">
+        <v>476</v>
+      </c>
+      <c r="C838" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="D838" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="839" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A839" s="1">
+        <v>46011</v>
+      </c>
+      <c r="B839" t="s">
+        <v>68</v>
+      </c>
+      <c r="C839" s="2">
+        <v>1.52</v>
+      </c>
+      <c r="D839" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="840" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A840" s="1">
+        <v>46011</v>
+      </c>
+      <c r="B840" t="s">
+        <v>477</v>
+      </c>
+      <c r="C840" s="2">
+        <v>10.9</v>
+      </c>
+      <c r="D840" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="841" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A841" s="1">
+        <v>46011</v>
+      </c>
+      <c r="B841" t="s">
+        <v>478</v>
+      </c>
+      <c r="C841" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="D841" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="842" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A842" s="1">
+        <v>46011</v>
+      </c>
+      <c r="B842" t="s">
+        <v>478</v>
+      </c>
+      <c r="C842" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="D842" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="843" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A843" s="1">
+        <v>46012</v>
+      </c>
+      <c r="B843" t="s">
+        <v>219</v>
+      </c>
+      <c r="C843" s="2">
+        <v>4</v>
+      </c>
+      <c r="D843" t="s">
         <v>22</v>
       </c>
     </row>
@@ -12777,7 +13827,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47AC92D9-8D81-4D6D-9D00-CF5410D2E104}">
-  <dimension ref="A2:I118"/>
+  <dimension ref="A2:I131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" customWidth="1"/>
@@ -13446,7 +14496,7 @@
     <row r="74" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B74" s="5"/>
       <c r="C74" s="10"/>
-      <c r="G74" s="24" t="s">
+      <c r="G74" s="26" t="s">
         <v>344</v>
       </c>
     </row>
@@ -13457,7 +14507,7 @@
       <c r="C75" s="10">
         <v>2.93</v>
       </c>
-      <c r="G75" s="24"/>
+      <c r="G75" s="26"/>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B76" s="3" t="s">
@@ -13466,7 +14516,7 @@
       <c r="C76" s="8">
         <v>2.5</v>
       </c>
-      <c r="G76" s="24"/>
+      <c r="G76" s="26"/>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B77" s="5" t="s">
@@ -13475,7 +14525,7 @@
       <c r="C77" s="10">
         <v>1</v>
       </c>
-      <c r="G77" s="24"/>
+      <c r="G77" s="26"/>
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B78" s="3" t="s">
@@ -13484,7 +14534,7 @@
       <c r="C78" s="8">
         <v>1.46</v>
       </c>
-      <c r="G78" s="24"/>
+      <c r="G78" s="26"/>
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B79" s="5" t="s">
@@ -13493,7 +14543,7 @@
       <c r="C79" s="10">
         <v>0.62</v>
       </c>
-      <c r="G79" s="24"/>
+      <c r="G79" s="26"/>
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B80" s="3" t="s">
@@ -13502,7 +14552,7 @@
       <c r="C80" s="8">
         <v>0.39</v>
       </c>
-      <c r="G80" s="24"/>
+      <c r="G80" s="26"/>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B81" s="5" t="s">
@@ -13511,7 +14561,7 @@
       <c r="C81" s="10">
         <v>7.72</v>
       </c>
-      <c r="G81" s="24"/>
+      <c r="G81" s="26"/>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B82" s="3" t="s">
@@ -13520,7 +14570,7 @@
       <c r="C82" s="8">
         <v>5.83</v>
       </c>
-      <c r="G82" s="24"/>
+      <c r="G82" s="26"/>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B83" s="5" t="s">
@@ -13529,7 +14579,7 @@
       <c r="C83" s="10">
         <v>3</v>
       </c>
-      <c r="G83" s="24"/>
+      <c r="G83" s="26"/>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B84" s="3" t="s">
@@ -13538,7 +14588,7 @@
       <c r="C84" s="8">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G84" s="24"/>
+      <c r="G84" s="26"/>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B85" s="5" t="s">
@@ -13547,7 +14597,7 @@
       <c r="C85" s="10">
         <v>3.2</v>
       </c>
-      <c r="G85" s="24"/>
+      <c r="G85" s="26"/>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B86" s="3" t="s">
@@ -13556,7 +14606,7 @@
       <c r="C86" s="8">
         <v>1.73</v>
       </c>
-      <c r="G86" s="24"/>
+      <c r="G86" s="26"/>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B87" s="5" t="s">
@@ -13565,7 +14615,7 @@
       <c r="C87" s="10">
         <v>6.2</v>
       </c>
-      <c r="G87" s="24"/>
+      <c r="G87" s="26"/>
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C88" s="11">
@@ -13754,6 +14804,93 @@
       <c r="D118">
         <f>SUM(D114:D117)</f>
         <v>9.02</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B122" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C122" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B123" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C123" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B124" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="C124" s="10">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B125" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C125" s="8">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B126" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C126" s="10">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B127" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C127" s="8">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
+        <v>342</v>
+      </c>
+      <c r="C128">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B129" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C129" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B130" t="s">
+        <v>480</v>
+      </c>
+      <c r="C130" s="25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C131" s="11">
+        <f>SUM(C122:C130)</f>
+        <v>62.589999999999996</v>
+      </c>
+      <c r="D131">
+        <f>52.59/5</f>
+        <v>10.518000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -13762,4 +14899,270 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE27A7CE-2C1C-40F2-A65A-01CB2E54A69C}">
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B1">
+        <v>800</v>
+      </c>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B2">
+        <v>21.4</v>
+      </c>
+      <c r="C2" s="24"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B3">
+        <v>48.8</v>
+      </c>
+      <c r="C3" s="24"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>428</v>
+      </c>
+      <c r="B4">
+        <v>17.64</v>
+      </c>
+      <c r="C4" s="24"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>430</v>
+      </c>
+      <c r="B5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>431</v>
+      </c>
+      <c r="B6">
+        <v>290</v>
+      </c>
+      <c r="C6" s="24"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>432</v>
+      </c>
+      <c r="B7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>433</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B9">
+        <v>250</v>
+      </c>
+      <c r="C9" s="24"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>435</v>
+      </c>
+      <c r="B10">
+        <v>150</v>
+      </c>
+      <c r="C10" s="24"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>438</v>
+      </c>
+      <c r="B11">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>439</v>
+      </c>
+      <c r="B12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>440</v>
+      </c>
+      <c r="B13">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>436</v>
+      </c>
+      <c r="B14">
+        <v>12.16</v>
+      </c>
+      <c r="C14" s="24"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>437</v>
+      </c>
+      <c r="B15">
+        <v>61.21</v>
+      </c>
+      <c r="C15" s="24"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>441</v>
+      </c>
+      <c r="B16">
+        <f>SUM(B1:B15)</f>
+        <v>3052.21</v>
+      </c>
+      <c r="D16">
+        <f>3300-3052.21</f>
+        <v>247.78999999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>442</v>
+      </c>
+      <c r="C17">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>441</v>
+      </c>
+      <c r="C18">
+        <v>2108.64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>443</v>
+      </c>
+      <c r="C19">
+        <f>C17-C18</f>
+        <v>-108.63999999999987</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>428</v>
+      </c>
+      <c r="B21">
+        <v>17.64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>430</v>
+      </c>
+      <c r="B22">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>431</v>
+      </c>
+      <c r="B23">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>432</v>
+      </c>
+      <c r="B24">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>433</v>
+      </c>
+      <c r="B25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>434</v>
+      </c>
+      <c r="B26">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>435</v>
+      </c>
+      <c r="B27">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>438</v>
+      </c>
+      <c r="B28">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>439</v>
+      </c>
+      <c r="B29">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>440</v>
+      </c>
+      <c r="B30">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B32">
+        <f>SUM(B21:B31)</f>
+        <v>2108.64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>